--- a/ARM Functions/Move Edits/Core Enforcer.xlsx
+++ b/ARM Functions/Move Edits/Core Enforcer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DE317F-8B24-4820-9D4D-E6587A8CE926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B19DE6-AAF6-437E-953D-25919C2E0FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="96">
   <si>
     <t>Address</t>
   </si>
@@ -281,12 +281,6 @@
     <t>push {r4, r5, r6, lr}</t>
   </si>
   <si>
-    <t>mov r4, r0</t>
-  </si>
-  <si>
-    <t>b 0x000D0FC0</t>
-  </si>
-  <si>
     <t>goto use highest attacking stat (middle since we already did a bunch of stuff)</t>
   </si>
   <si>
@@ -296,24 +290,6 @@
     <t>0200A0E3</t>
   </si>
   <si>
-    <t>BD17FEEB</t>
-  </si>
-  <si>
-    <t>8841FEEB</t>
-  </si>
-  <si>
-    <t>0040A0E1</t>
-  </si>
-  <si>
-    <t>C654FFEB</t>
-  </si>
-  <si>
-    <t>A87AFDEB</t>
-  </si>
-  <si>
-    <t>CA3CFFEA</t>
-  </si>
-  <si>
     <t>7080BDE8</t>
   </si>
   <si>
@@ -324,6 +300,30 @@
   </si>
   <si>
     <t>Use highest attacking stat, also set Animation 1 if Mega/Ultra 0x2D</t>
+  </si>
+  <si>
+    <t>b 0x000D0FB0</t>
+  </si>
+  <si>
+    <t>00102850</t>
+  </si>
+  <si>
+    <t>BC14FEEB</t>
+  </si>
+  <si>
+    <t>0900001A</t>
+  </si>
+  <si>
+    <t>873EFEEB</t>
+  </si>
+  <si>
+    <t>C651FFEB</t>
+  </si>
+  <si>
+    <t>A877FDEB</t>
+  </si>
+  <si>
+    <t>C639FFEA</t>
   </si>
 </sst>
 </file>
@@ -774,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D33247EB-EDD1-4FB4-BA08-1D454B2F7DD3}">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="12.2109375" style="2" customWidth="1"/>
@@ -886,16 +886,15 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A76)+4,8)</f>
-        <v>00101C4C</v>
+      <c r="A13" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>80</v>
@@ -903,8 +902,8 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="str">
-        <f t="shared" ref="A14:A31" si="1">DEC2HEX(HEX2DEC(A13)+4,8)</f>
-        <v>00101C50</v>
+        <f t="shared" ref="A14:A30" si="1">DEC2HEX(HEX2DEC(A13)+4,8)</f>
+        <v>00102854</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -916,7 +915,7 @@
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>00101C54</v>
+        <v>00102858</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
@@ -928,10 +927,10 @@
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>00101C58</v>
+        <v>0010285C</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>79</v>
@@ -943,10 +942,10 @@
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>00101C5C</v>
+        <v>00102860</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>22</v>
@@ -956,7 +955,7 @@
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>00101C60</v>
+        <v>00102864</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>19</v>
@@ -969,21 +968,21 @@
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>00101C64</v>
+        <v>00102868</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$31)</f>
-        <v>bne 0x00101C94</v>
+        <f>_xlfn.CONCAT("bne 0x",A$30)</f>
+        <v>bne 0x00102894</v>
       </c>
       <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>00101C68</v>
+        <v>0010286C</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>21</v>
@@ -998,7 +997,7 @@
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>00101C6C</v>
+        <v>00102870</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>23</v>
@@ -1011,10 +1010,10 @@
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>00101C70</v>
+        <v>00102874</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>25</v>
@@ -1022,687 +1021,674 @@
       <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>00101C74</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>00102878</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>00101C78</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>89</v>
+        <v>0010287C</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>35</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>00101C7C</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="10"/>
+        <v>00102880</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="10" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$29)</f>
+        <v>bne 0x00102890</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="10" t="str">
+      <c r="A26" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>00101C80</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" s="10" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$30)</f>
-        <v>bne 0x00101C90</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>93</v>
+        <v>00102884</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>00101C84</v>
+        <v>00102888</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>77</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>00101C88</v>
+        <v>0010288C</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="8" t="str">
+      <c r="A29" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>00101C8C</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="8"/>
+        <v>00102890</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="19" t="str">
+      <c r="A30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>00101C90</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101C94</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="2" t="str">
+        <v>00102894</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(C13,"push","pop"),"lr","pc")</f>
         <v>pop {r4, r5, r6, pc}</v>
       </c>
     </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
+      <c r="A33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>53</v>
+      <c r="A34" s="2" t="str">
+        <f t="shared" ref="A34:A51" si="2">DEC2HEX(HEX2DEC(A33)+4,8)</f>
+        <v>00101BAC</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="str">
-        <f t="shared" ref="A35:A52" si="2">DEC2HEX(HEX2DEC(A34)+4,8)</f>
-        <v>00101BAC</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>00101BB0</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>00101BB4</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>00101BB4</v>
+        <v>00101BB8</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>00101BB8</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>22</v>
+        <v>00101BBC</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>00101BBC</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>18</v>
+        <v>00101BC0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$51)</f>
+        <v>bne 0x00101BF0</v>
       </c>
       <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="6" t="str">
+      <c r="A40" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>00101BC0</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$52)</f>
-        <v>bne 0x00101BF0</v>
-      </c>
-      <c r="D40" s="6"/>
+        <v>00101BC4</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>00101BC4</v>
+        <v>00101BC8</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>00101BC8</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>23</v>
+        <v>00101BCC</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>00101BCC</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="4"/>
+        <v>00101BD0</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>00101BD0</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>59</v>
+        <v>00101BD4</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>35</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D44" s="10"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>00101BD4</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>30</v>
+        <v>00101BD8</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="10" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$51)</f>
+        <v>bne 0x00101BF0</v>
       </c>
       <c r="D45" s="10"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="10" t="str">
+      <c r="A46" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BD8</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" s="10" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$52)</f>
-        <v>bne 0x00101BF0</v>
-      </c>
-      <c r="D46" s="10"/>
+        <v>00101BDC</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BDC</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>61</v>
+        <v>00101BE0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BE0</v>
+        <v>00101BE4</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BE4</v>
+        <v>00101BE8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="C49" s="2" t="str">
+        <f>SUBSTITUTE(C33,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BE8</v>
+        <v>00101BEC</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="2" t="str">
-        <f>SUBSTITUTE(C34,"push","pop")</f>
-        <v>pop {r4, r5, lr}</v>
+        <v>65</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>00101BEC</v>
+        <v>00101BF0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>13</v>
+        <v>66</v>
+      </c>
+      <c r="C51" s="2" t="str">
+        <f>SUBSTITUTE(C49,"lr","pc")</f>
+        <v>pop {r4, r5, pc}</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>00101BF0</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="2" t="str">
-        <f>SUBSTITUTE(C50,"lr","pc")</f>
-        <v>pop {r4, r5, pc}</v>
-      </c>
+      <c r="B52" s="13"/>
+      <c r="D52" s="9"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="B53" s="13"/>
-      <c r="D53" s="9"/>
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="14"/>
+      <c r="A54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="2" t="s">
-        <v>54</v>
+      <c r="A55" s="2" t="str">
+        <f t="shared" ref="A55:A75" si="3">DEC2HEX(HEX2DEC(A54)+4,8)</f>
+        <v>00101BF8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="str">
-        <f t="shared" ref="A56:A76" si="3">DEC2HEX(HEX2DEC(A55)+4,8)</f>
-        <v>00101BF8</v>
+        <f t="shared" si="3"/>
+        <v>00101BFC</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>00101BFC</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>16</v>
+      <c r="A57" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C00</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>00101C00</v>
+        <v>00101C04</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>00101C04</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>22</v>
+        <v>00101C08</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>00101C08</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>18</v>
+        <v>00101C0C</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="7" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$75)</f>
+        <v>bne 0x00101C48</v>
       </c>
       <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C0C</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="7" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$76)</f>
-        <v>bne 0x00101C48</v>
-      </c>
-      <c r="D61" s="6"/>
+      <c r="A61" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C10</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>00101C10</v>
+        <v>00101C14</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>00101C14</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>23</v>
+        <v>00101C18</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D63" s="4"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C18</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D64" s="4"/>
+      <c r="A64" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C1C</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>00101C1C</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>70</v>
+        <v>00101C20</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>35</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D65" s="10"/>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>00101C20</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>30</v>
+        <v>00101C24</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="10" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$75)</f>
+        <v>bne 0x00101C48</v>
       </c>
       <c r="D66" s="10"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C24</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="10" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$76)</f>
-        <v>bne 0x00101C48</v>
-      </c>
-      <c r="D67" s="10"/>
+      <c r="A67" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C28</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>00101C28</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>42</v>
+        <v>00101C2C</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>44</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D68" s="15"/>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>00101C2C</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" s="15"/>
+        <v>00101C30</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>00101C30</v>
+        <v>00101C34</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>45</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C70" s="15" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$75)</f>
+        <v>bne 0x00101C48</v>
+      </c>
+      <c r="D70" s="15"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C34</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C71" s="15" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$76)</f>
-        <v>bne 0x00101C48</v>
-      </c>
-      <c r="D71" s="15"/>
+      <c r="A71" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C38</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>00101C38</v>
+        <v>00101C3C</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D72" s="8"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C3C</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D73" s="8"/>
+      <c r="A73" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C40</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="2" t="str">
+        <f>SUBSTITUTE(C54,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
+      </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C40</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="2" t="str">
-        <f>SUBSTITUTE(C55,"push","pop")</f>
-        <v>pop {r4, r5, lr}</v>
-      </c>
+      <c r="A74" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>00101C44</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>00101C44</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="8"/>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="2" t="str">
+      <c r="A75" s="2" t="str">
         <f t="shared" si="3"/>
         <v>00101C48</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C76" s="2" t="str">
-        <f>SUBSTITUTE(C74,"lr","pc")</f>
+      <c r="C75" s="2" t="str">
+        <f>SUBSTITUTE(C73,"lr","pc")</f>
         <v>pop {r4, r5, pc}</v>
       </c>
     </row>

--- a/ARM Functions/Move Edits/Core Enforcer.xlsx
+++ b/ARM Functions/Move Edits/Core Enforcer.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B19DE6-AAF6-437E-953D-25919C2E0FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="code" sheetId="12" r:id="rId1"/>
